--- a/artfynd/Avvanm 36411 artfynd.xlsx
+++ b/artfynd/Avvanm 36411 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY228"/>
+  <dimension ref="A1:AY230"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13034,45 +13034,45 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>118682692</v>
+        <v>135058986</v>
       </c>
       <c r="B124" t="n">
-        <v>91872</v>
+        <v>91995</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5447</v>
+        <v>5442</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Lars-Klemetmyran, Pi lm</t>
+          <t>Åberget, Pi lm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>696974</v>
+        <v>696957</v>
       </c>
       <c r="R124" t="n">
-        <v>7323636</v>
+        <v>7323656</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13099,12 +13099,17 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13119,64 +13124,60 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY124" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>118682765</v>
+        <v>135058987</v>
       </c>
       <c r="B125" t="n">
-        <v>91872</v>
+        <v>91995</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5447</v>
+        <v>5442</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>..., Pi lm</t>
+          <t>Åberget, Pi lm</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>697012</v>
+        <v>696920</v>
       </c>
       <c r="R125" t="n">
-        <v>7323651</v>
+        <v>7323571</v>
       </c>
       <c r="S125" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -13200,12 +13201,17 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2024-07-25</t>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13220,48 +13226,44 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
-        </is>
-      </c>
-      <c r="AY125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
-        </is>
-      </c>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>118682923</v>
+        <v>118682692</v>
       </c>
       <c r="B126" t="n">
-        <v>93223</v>
+        <v>91872</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>5448</v>
+        <v>5447</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13271,10 +13273,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>696990</v>
+        <v>696974</v>
       </c>
       <c r="R126" t="n">
-        <v>7323731</v>
+        <v>7323636</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13321,12 +13323,12 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Julia Lea Falk, Brian Johnson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr">
@@ -13337,10 +13339,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>118671533</v>
+        <v>118682765</v>
       </c>
       <c r="B127" t="n">
-        <v>91282</v>
+        <v>91872</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -13348,37 +13350,37 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5685</v>
+        <v>5447</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Anna-Lisabäcken, Anna-Lisabäcken, Pi lm</t>
+          <t>..., Pi lm</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>696845</v>
+        <v>697012</v>
       </c>
       <c r="R127" t="n">
-        <v>7323632</v>
+        <v>7323651</v>
       </c>
       <c r="S127" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -13422,12 +13424,12 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Alexander Singer, Brian Johnson, Daniel Rutschman, Torun Ingrid Maria Jacobsson, Julia Lea Falk, Lisa Requin, Sofia Hamrin, Michaela Ehmann, Evalena Sköld, Tyr Nilsson, Bertil Svensson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr">
@@ -13438,48 +13440,48 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>118683786</v>
+        <v>118682923</v>
       </c>
       <c r="B128" t="n">
-        <v>79351</v>
+        <v>93223</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6434</v>
+        <v>5448</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Lars-Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>696838</v>
+        <v>696990</v>
       </c>
       <c r="R128" t="n">
-        <v>7323602</v>
+        <v>7323731</v>
       </c>
       <c r="S128" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13523,12 +13525,12 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Julia Lea Falk, Brian Johnson</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr">
@@ -13539,45 +13541,45 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>118682718</v>
+        <v>118671533</v>
       </c>
       <c r="B129" t="n">
-        <v>78730</v>
+        <v>91282</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6437</v>
+        <v>5685</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Lars-Klemetmyran, Pi lm</t>
+          <t>Anna-Lisabäcken, Anna-Lisabäcken, Pi lm</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>697024</v>
+        <v>696845</v>
       </c>
       <c r="R129" t="n">
-        <v>7323624</v>
+        <v>7323632</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13624,12 +13626,12 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Alexander Singer, Brian Johnson, Daniel Rutschman, Torun Ingrid Maria Jacobsson, Julia Lea Falk, Lisa Requin, Sofia Hamrin, Michaela Ehmann, Evalena Sköld, Tyr Nilsson, Bertil Svensson</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr">
@@ -13640,45 +13642,45 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>118682776</v>
+        <v>118683786</v>
       </c>
       <c r="B130" t="n">
-        <v>78730</v>
+        <v>79351</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6437</v>
+        <v>6434</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>..., Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>696978</v>
+        <v>696838</v>
       </c>
       <c r="R130" t="n">
-        <v>7323682</v>
+        <v>7323602</v>
       </c>
       <c r="S130" t="n">
         <v>15</v>
@@ -13719,19 +13721,18 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr">
@@ -13742,7 +13743,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>118682821</v>
+        <v>118682718</v>
       </c>
       <c r="B131" t="n">
         <v>78730</v>
@@ -13773,17 +13774,17 @@
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Lars-Klemets Myren, Pi lm</t>
+          <t>Lars-Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>696870</v>
+        <v>697024</v>
       </c>
       <c r="R131" t="n">
-        <v>7323489</v>
+        <v>7323624</v>
       </c>
       <c r="S131" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -13827,12 +13828,12 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr">
@@ -13843,7 +13844,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>118682823</v>
+        <v>118682776</v>
       </c>
       <c r="B132" t="n">
         <v>78730</v>
@@ -13874,14 +13875,14 @@
       <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Lars-Klemets Myren, Pi lm</t>
+          <t>..., Pi lm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>697077</v>
+        <v>696978</v>
       </c>
       <c r="R132" t="n">
-        <v>7323757</v>
+        <v>7323682</v>
       </c>
       <c r="S132" t="n">
         <v>15</v>
@@ -13922,18 +13923,19 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr">
@@ -13944,7 +13946,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>118682824</v>
+        <v>118682821</v>
       </c>
       <c r="B133" t="n">
         <v>78730</v>
@@ -13979,10 +13981,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>696977</v>
+        <v>696870</v>
       </c>
       <c r="R133" t="n">
-        <v>7323784</v>
+        <v>7323489</v>
       </c>
       <c r="S133" t="n">
         <v>15</v>
@@ -14045,7 +14047,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>118682826</v>
+        <v>118682823</v>
       </c>
       <c r="B134" t="n">
         <v>78730</v>
@@ -14080,10 +14082,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>696936</v>
+        <v>697077</v>
       </c>
       <c r="R134" t="n">
-        <v>7323719</v>
+        <v>7323757</v>
       </c>
       <c r="S134" t="n">
         <v>15</v>
@@ -14146,7 +14148,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>118682827</v>
+        <v>118682824</v>
       </c>
       <c r="B135" t="n">
         <v>78730</v>
@@ -14181,10 +14183,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>696890</v>
+        <v>696977</v>
       </c>
       <c r="R135" t="n">
-        <v>7323617</v>
+        <v>7323784</v>
       </c>
       <c r="S135" t="n">
         <v>15</v>
@@ -14247,7 +14249,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>118682829</v>
+        <v>118682826</v>
       </c>
       <c r="B136" t="n">
         <v>78730</v>
@@ -14282,10 +14284,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>696865</v>
+        <v>696936</v>
       </c>
       <c r="R136" t="n">
-        <v>7323645</v>
+        <v>7323719</v>
       </c>
       <c r="S136" t="n">
         <v>15</v>
@@ -14348,7 +14350,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>118682943</v>
+        <v>118682827</v>
       </c>
       <c r="B137" t="n">
         <v>78730</v>
@@ -14379,17 +14381,17 @@
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Lars-Klemetmyran, Pi lm</t>
+          <t>Lars-Klemets Myren, Pi lm</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>696876</v>
+        <v>696890</v>
       </c>
       <c r="R137" t="n">
-        <v>7323769</v>
+        <v>7323617</v>
       </c>
       <c r="S137" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -14433,12 +14435,12 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Julia Lea Falk, Brian Johnson</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
@@ -14449,7 +14451,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>118682944</v>
+        <v>118682829</v>
       </c>
       <c r="B138" t="n">
         <v>78730</v>
@@ -14480,17 +14482,17 @@
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Lars-Klemetmyran, Pi lm</t>
+          <t>Lars-Klemets Myren, Pi lm</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>696872</v>
+        <v>696865</v>
       </c>
       <c r="R138" t="n">
-        <v>7323693</v>
+        <v>7323645</v>
       </c>
       <c r="S138" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -14534,12 +14536,12 @@
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Julia Lea Falk, Brian Johnson</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
@@ -14550,7 +14552,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>118683010</v>
+        <v>118682943</v>
       </c>
       <c r="B139" t="n">
         <v>78730</v>
@@ -14579,22 +14581,19 @@
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Lars Klemet myran, Pi lm</t>
+          <t>Lars-Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>696992</v>
+        <v>696876</v>
       </c>
       <c r="R139" t="n">
-        <v>7323563</v>
+        <v>7323769</v>
       </c>
       <c r="S139" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -14632,19 +14631,18 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
-      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Julia Lea Falk, Brian Johnson</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
@@ -14655,7 +14653,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>118683021</v>
+        <v>118682944</v>
       </c>
       <c r="B140" t="n">
         <v>78730</v>
@@ -14686,17 +14684,17 @@
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Lars Klemet myran, Pi lm</t>
+          <t>Lars-Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>696832</v>
+        <v>696872</v>
       </c>
       <c r="R140" t="n">
-        <v>7323503</v>
+        <v>7323693</v>
       </c>
       <c r="S140" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -14734,19 +14732,18 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Julia Lea Falk, Brian Johnson</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
@@ -14757,7 +14754,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>118683022</v>
+        <v>118683010</v>
       </c>
       <c r="B141" t="n">
         <v>78730</v>
@@ -14786,16 +14783,19 @@
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
           <t>Lars Klemet myran, Pi lm</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>697008</v>
+        <v>696992</v>
       </c>
       <c r="R141" t="n">
-        <v>7323621</v>
+        <v>7323563</v>
       </c>
       <c r="S141" t="n">
         <v>15</v>
@@ -14859,7 +14859,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>118683023</v>
+        <v>118683021</v>
       </c>
       <c r="B142" t="n">
         <v>78730</v>
@@ -14894,10 +14894,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>697097</v>
+        <v>696832</v>
       </c>
       <c r="R142" t="n">
-        <v>7323675</v>
+        <v>7323503</v>
       </c>
       <c r="S142" t="n">
         <v>15</v>
@@ -14961,7 +14961,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>118683024</v>
+        <v>118683022</v>
       </c>
       <c r="B143" t="n">
         <v>78730</v>
@@ -14996,10 +14996,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>696964</v>
+        <v>697008</v>
       </c>
       <c r="R143" t="n">
-        <v>7323642</v>
+        <v>7323621</v>
       </c>
       <c r="S143" t="n">
         <v>15</v>
@@ -15063,7 +15063,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>118683025</v>
+        <v>118683023</v>
       </c>
       <c r="B144" t="n">
         <v>78730</v>
@@ -15098,10 +15098,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>696939</v>
+        <v>697097</v>
       </c>
       <c r="R144" t="n">
-        <v>7323649</v>
+        <v>7323675</v>
       </c>
       <c r="S144" t="n">
         <v>15</v>
@@ -15165,7 +15165,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>118683026</v>
+        <v>118683024</v>
       </c>
       <c r="B145" t="n">
         <v>78730</v>
@@ -15200,10 +15200,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>696899</v>
+        <v>696964</v>
       </c>
       <c r="R145" t="n">
-        <v>7323660</v>
+        <v>7323642</v>
       </c>
       <c r="S145" t="n">
         <v>15</v>
@@ -15267,7 +15267,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>118683028</v>
+        <v>118683025</v>
       </c>
       <c r="B146" t="n">
         <v>78730</v>
@@ -15302,10 +15302,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>696825</v>
+        <v>696939</v>
       </c>
       <c r="R146" t="n">
-        <v>7323668</v>
+        <v>7323649</v>
       </c>
       <c r="S146" t="n">
         <v>15</v>
@@ -15369,7 +15369,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>118683811</v>
+        <v>118683026</v>
       </c>
       <c r="B147" t="n">
         <v>78730</v>
@@ -15400,14 +15400,14 @@
       <c r="I147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Lars Klemet myran, Pi lm</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>696840</v>
+        <v>696899</v>
       </c>
       <c r="R147" t="n">
-        <v>7323551</v>
+        <v>7323660</v>
       </c>
       <c r="S147" t="n">
         <v>15</v>
@@ -15448,18 +15448,19 @@
       <c r="AE147" t="b">
         <v>0</v>
       </c>
+      <c r="AF147" t="inlineStr"/>
       <c r="AG147" t="b">
         <v>0</v>
       </c>
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
@@ -15470,7 +15471,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>118683812</v>
+        <v>118683028</v>
       </c>
       <c r="B148" t="n">
         <v>78730</v>
@@ -15501,14 +15502,14 @@
       <c r="I148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Lars Klemet myran, Pi lm</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>696888</v>
+        <v>696825</v>
       </c>
       <c r="R148" t="n">
-        <v>7323531</v>
+        <v>7323668</v>
       </c>
       <c r="S148" t="n">
         <v>15</v>
@@ -15549,18 +15550,19 @@
       <c r="AE148" t="b">
         <v>0</v>
       </c>
+      <c r="AF148" t="inlineStr"/>
       <c r="AG148" t="b">
         <v>0</v>
       </c>
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
@@ -15571,7 +15573,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>118683813</v>
+        <v>118683811</v>
       </c>
       <c r="B149" t="n">
         <v>78730</v>
@@ -15606,10 +15608,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>696906</v>
+        <v>696840</v>
       </c>
       <c r="R149" t="n">
-        <v>7323534</v>
+        <v>7323551</v>
       </c>
       <c r="S149" t="n">
         <v>15</v>
@@ -15672,7 +15674,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>118683814</v>
+        <v>118683812</v>
       </c>
       <c r="B150" t="n">
         <v>78730</v>
@@ -15707,10 +15709,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>696963</v>
+        <v>696888</v>
       </c>
       <c r="R150" t="n">
-        <v>7323514</v>
+        <v>7323531</v>
       </c>
       <c r="S150" t="n">
         <v>15</v>
@@ -15773,7 +15775,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>118683815</v>
+        <v>118683813</v>
       </c>
       <c r="B151" t="n">
         <v>78730</v>
@@ -15808,10 +15810,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>697006</v>
+        <v>696906</v>
       </c>
       <c r="R151" t="n">
-        <v>7323539</v>
+        <v>7323534</v>
       </c>
       <c r="S151" t="n">
         <v>15</v>
@@ -15874,7 +15876,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>118683816</v>
+        <v>118683814</v>
       </c>
       <c r="B152" t="n">
         <v>78730</v>
@@ -15909,10 +15911,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>697029</v>
+        <v>696963</v>
       </c>
       <c r="R152" t="n">
-        <v>7323565</v>
+        <v>7323514</v>
       </c>
       <c r="S152" t="n">
         <v>15</v>
@@ -15975,7 +15977,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>118683817</v>
+        <v>118683815</v>
       </c>
       <c r="B153" t="n">
         <v>78730</v>
@@ -16010,10 +16012,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>697028</v>
+        <v>697006</v>
       </c>
       <c r="R153" t="n">
-        <v>7323644</v>
+        <v>7323539</v>
       </c>
       <c r="S153" t="n">
         <v>15</v>
@@ -16076,7 +16078,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>118683818</v>
+        <v>118683816</v>
       </c>
       <c r="B154" t="n">
         <v>78730</v>
@@ -16111,10 +16113,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>697096</v>
+        <v>697029</v>
       </c>
       <c r="R154" t="n">
-        <v>7323681</v>
+        <v>7323565</v>
       </c>
       <c r="S154" t="n">
         <v>15</v>
@@ -16177,7 +16179,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>118683820</v>
+        <v>118683817</v>
       </c>
       <c r="B155" t="n">
         <v>78730</v>
@@ -16212,10 +16214,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>697094</v>
+        <v>697028</v>
       </c>
       <c r="R155" t="n">
-        <v>7323695</v>
+        <v>7323644</v>
       </c>
       <c r="S155" t="n">
         <v>15</v>
@@ -16278,7 +16280,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>118683821</v>
+        <v>118683818</v>
       </c>
       <c r="B156" t="n">
         <v>78730</v>
@@ -16313,10 +16315,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>697026</v>
+        <v>697096</v>
       </c>
       <c r="R156" t="n">
-        <v>7323766</v>
+        <v>7323681</v>
       </c>
       <c r="S156" t="n">
         <v>15</v>
@@ -16379,7 +16381,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>118683822</v>
+        <v>118683820</v>
       </c>
       <c r="B157" t="n">
         <v>78730</v>
@@ -16414,10 +16416,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>697008</v>
+        <v>697094</v>
       </c>
       <c r="R157" t="n">
-        <v>7323758</v>
+        <v>7323695</v>
       </c>
       <c r="S157" t="n">
         <v>15</v>
@@ -16480,7 +16482,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>118683823</v>
+        <v>118683821</v>
       </c>
       <c r="B158" t="n">
         <v>78730</v>
@@ -16515,10 +16517,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>696962</v>
+        <v>697026</v>
       </c>
       <c r="R158" t="n">
-        <v>7323691</v>
+        <v>7323766</v>
       </c>
       <c r="S158" t="n">
         <v>15</v>
@@ -16581,7 +16583,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>118683824</v>
+        <v>118683822</v>
       </c>
       <c r="B159" t="n">
         <v>78730</v>
@@ -16616,10 +16618,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>696905</v>
+        <v>697008</v>
       </c>
       <c r="R159" t="n">
-        <v>7323662</v>
+        <v>7323758</v>
       </c>
       <c r="S159" t="n">
         <v>15</v>
@@ -16682,7 +16684,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>118683826</v>
+        <v>118683823</v>
       </c>
       <c r="B160" t="n">
         <v>78730</v>
@@ -16717,10 +16719,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>696900</v>
+        <v>696962</v>
       </c>
       <c r="R160" t="n">
-        <v>7323650</v>
+        <v>7323691</v>
       </c>
       <c r="S160" t="n">
         <v>15</v>
@@ -16783,7 +16785,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>118683827</v>
+        <v>118683824</v>
       </c>
       <c r="B161" t="n">
         <v>78730</v>
@@ -16818,10 +16820,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>696832</v>
+        <v>696905</v>
       </c>
       <c r="R161" t="n">
-        <v>7323578</v>
+        <v>7323662</v>
       </c>
       <c r="S161" t="n">
         <v>15</v>
@@ -16884,7 +16886,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>118683828</v>
+        <v>118683826</v>
       </c>
       <c r="B162" t="n">
         <v>78730</v>
@@ -16919,10 +16921,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>696832</v>
+        <v>696900</v>
       </c>
       <c r="R162" t="n">
-        <v>7323593</v>
+        <v>7323650</v>
       </c>
       <c r="S162" t="n">
         <v>15</v>
@@ -16985,7 +16987,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>118684521</v>
+        <v>118683827</v>
       </c>
       <c r="B163" t="n">
         <v>78730</v>
@@ -17016,17 +17018,17 @@
       <c r="I163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Larsklemetmyran, Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>697033</v>
+        <v>696832</v>
       </c>
       <c r="R163" t="n">
-        <v>7323654</v>
+        <v>7323578</v>
       </c>
       <c r="S163" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -17070,12 +17072,12 @@
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
@@ -17086,7 +17088,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>118684523</v>
+        <v>118683828</v>
       </c>
       <c r="B164" t="n">
         <v>78730</v>
@@ -17117,17 +17119,17 @@
       <c r="I164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Larsklemetmyran, Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>696848</v>
+        <v>696832</v>
       </c>
       <c r="R164" t="n">
-        <v>7323640</v>
+        <v>7323593</v>
       </c>
       <c r="S164" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -17171,12 +17173,12 @@
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
@@ -17187,7 +17189,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>118686849</v>
+        <v>118684521</v>
       </c>
       <c r="B165" t="n">
         <v>78730</v>
@@ -17218,17 +17220,17 @@
       <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Avvanm, Pi lm</t>
+          <t>Larsklemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>696823</v>
+        <v>697033</v>
       </c>
       <c r="R165" t="n">
-        <v>7323579</v>
+        <v>7323654</v>
       </c>
       <c r="S165" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -17272,12 +17274,12 @@
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
@@ -17288,7 +17290,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>118686850</v>
+        <v>118684523</v>
       </c>
       <c r="B166" t="n">
         <v>78730</v>
@@ -17319,17 +17321,17 @@
       <c r="I166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Avvanm, Pi lm</t>
+          <t>Larsklemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>696841</v>
+        <v>696848</v>
       </c>
       <c r="R166" t="n">
-        <v>7323544</v>
+        <v>7323640</v>
       </c>
       <c r="S166" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -17373,12 +17375,12 @@
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr">
@@ -17389,7 +17391,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>118686851</v>
+        <v>118686849</v>
       </c>
       <c r="B167" t="n">
         <v>78730</v>
@@ -17424,10 +17426,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>696925</v>
+        <v>696823</v>
       </c>
       <c r="R167" t="n">
-        <v>7323592</v>
+        <v>7323579</v>
       </c>
       <c r="S167" t="n">
         <v>1</v>
@@ -17490,7 +17492,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>118686852</v>
+        <v>118686850</v>
       </c>
       <c r="B168" t="n">
         <v>78730</v>
@@ -17525,10 +17527,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>696876</v>
+        <v>696841</v>
       </c>
       <c r="R168" t="n">
-        <v>7323595</v>
+        <v>7323544</v>
       </c>
       <c r="S168" t="n">
         <v>1</v>
@@ -17591,10 +17593,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>118683003</v>
+        <v>118686851</v>
       </c>
       <c r="B169" t="n">
-        <v>83307</v>
+        <v>78730</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -17602,37 +17604,37 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6440</v>
+        <v>6437</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>Lars Klemet myran, Pi lm</t>
+          <t>Avvanm, Pi lm</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>696944</v>
+        <v>696925</v>
       </c>
       <c r="R169" t="n">
-        <v>7323506</v>
+        <v>7323592</v>
       </c>
       <c r="S169" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T169" t="inlineStr">
         <is>
@@ -17676,12 +17678,12 @@
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
@@ -17692,10 +17694,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>118682927</v>
+        <v>118686852</v>
       </c>
       <c r="B170" t="n">
-        <v>79084</v>
+        <v>78730</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -17703,37 +17705,37 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6446</v>
+        <v>6437</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
       <c r="P170" t="inlineStr">
         <is>
-          <t>Lars-Klemetmyran, Pi lm</t>
+          <t>Avvanm, Pi lm</t>
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>696916</v>
+        <v>696876</v>
       </c>
       <c r="R170" t="n">
-        <v>7323795</v>
+        <v>7323595</v>
       </c>
       <c r="S170" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T170" t="inlineStr">
         <is>
@@ -17777,12 +17779,12 @@
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>Julia Lea Falk, Brian Johnson</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr">
@@ -17793,10 +17795,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>118682766</v>
+        <v>118683003</v>
       </c>
       <c r="B171" t="n">
-        <v>79946</v>
+        <v>83307</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -17804,34 +17806,34 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>6453</v>
+        <v>6440</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>..., Pi lm</t>
+          <t>Lars Klemet myran, Pi lm</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>696993</v>
+        <v>696944</v>
       </c>
       <c r="R171" t="n">
-        <v>7323679</v>
+        <v>7323506</v>
       </c>
       <c r="S171" t="n">
         <v>15</v>
@@ -17878,12 +17880,12 @@
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr">
@@ -17894,10 +17896,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>118682915</v>
+        <v>118682927</v>
       </c>
       <c r="B172" t="n">
-        <v>79946</v>
+        <v>79084</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -17905,21 +17907,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -17929,10 +17931,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>696914</v>
+        <v>696916</v>
       </c>
       <c r="R172" t="n">
-        <v>7323793</v>
+        <v>7323795</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -17984,7 +17986,7 @@
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Julia Lea Falk, Brian Johnson</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
@@ -17995,7 +17997,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>118683004</v>
+        <v>118682766</v>
       </c>
       <c r="B173" t="n">
         <v>79946</v>
@@ -18026,14 +18028,14 @@
       <c r="I173" t="inlineStr"/>
       <c r="P173" t="inlineStr">
         <is>
-          <t>Lars Klemet myran, Pi lm</t>
+          <t>..., Pi lm</t>
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>696832</v>
+        <v>696993</v>
       </c>
       <c r="R173" t="n">
-        <v>7323503</v>
+        <v>7323679</v>
       </c>
       <c r="S173" t="n">
         <v>15</v>
@@ -18080,12 +18082,12 @@
       <c r="AT173" t="inlineStr"/>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
@@ -18096,7 +18098,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>118683005</v>
+        <v>118682915</v>
       </c>
       <c r="B174" t="n">
         <v>79946</v>
@@ -18127,17 +18129,17 @@
       <c r="I174" t="inlineStr"/>
       <c r="P174" t="inlineStr">
         <is>
-          <t>Lars Klemet myran, Pi lm</t>
+          <t>Lars-Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>696924</v>
+        <v>696914</v>
       </c>
       <c r="R174" t="n">
-        <v>7323510</v>
+        <v>7323793</v>
       </c>
       <c r="S174" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T174" t="inlineStr">
         <is>
@@ -18181,12 +18183,12 @@
       <c r="AT174" t="inlineStr"/>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr">
@@ -18197,7 +18199,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>118683758</v>
+        <v>118683004</v>
       </c>
       <c r="B175" t="n">
         <v>79946</v>
@@ -18228,14 +18230,14 @@
       <c r="I175" t="inlineStr"/>
       <c r="P175" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Lars Klemet myran, Pi lm</t>
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>696843</v>
+        <v>696832</v>
       </c>
       <c r="R175" t="n">
-        <v>7323526</v>
+        <v>7323503</v>
       </c>
       <c r="S175" t="n">
         <v>15</v>
@@ -18282,12 +18284,12 @@
       <c r="AT175" t="inlineStr"/>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
@@ -18298,7 +18300,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>118683760</v>
+        <v>118683005</v>
       </c>
       <c r="B176" t="n">
         <v>79946</v>
@@ -18329,14 +18331,14 @@
       <c r="I176" t="inlineStr"/>
       <c r="P176" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Lars Klemet myran, Pi lm</t>
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>696860</v>
+        <v>696924</v>
       </c>
       <c r="R176" t="n">
-        <v>7323545</v>
+        <v>7323510</v>
       </c>
       <c r="S176" t="n">
         <v>15</v>
@@ -18383,12 +18385,12 @@
       <c r="AT176" t="inlineStr"/>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr">
@@ -18399,7 +18401,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>118683761</v>
+        <v>118683758</v>
       </c>
       <c r="B177" t="n">
         <v>79946</v>
@@ -18434,10 +18436,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>697007</v>
+        <v>696843</v>
       </c>
       <c r="R177" t="n">
-        <v>7323538</v>
+        <v>7323526</v>
       </c>
       <c r="S177" t="n">
         <v>15</v>
@@ -18500,7 +18502,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>118683762</v>
+        <v>118683760</v>
       </c>
       <c r="B178" t="n">
         <v>79946</v>
@@ -18535,10 +18537,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>697090</v>
+        <v>696860</v>
       </c>
       <c r="R178" t="n">
-        <v>7323699</v>
+        <v>7323545</v>
       </c>
       <c r="S178" t="n">
         <v>15</v>
@@ -18601,7 +18603,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>118683763</v>
+        <v>118683761</v>
       </c>
       <c r="B179" t="n">
         <v>79946</v>
@@ -18636,10 +18638,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>697027</v>
+        <v>697007</v>
       </c>
       <c r="R179" t="n">
-        <v>7323770</v>
+        <v>7323538</v>
       </c>
       <c r="S179" t="n">
         <v>15</v>
@@ -18702,7 +18704,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>118683764</v>
+        <v>118683762</v>
       </c>
       <c r="B180" t="n">
         <v>79946</v>
@@ -18737,10 +18739,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>697005</v>
+        <v>697090</v>
       </c>
       <c r="R180" t="n">
-        <v>7323759</v>
+        <v>7323699</v>
       </c>
       <c r="S180" t="n">
         <v>15</v>
@@ -18803,7 +18805,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>118683765</v>
+        <v>118683763</v>
       </c>
       <c r="B181" t="n">
         <v>79946</v>
@@ -18838,10 +18840,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>696852</v>
+        <v>697027</v>
       </c>
       <c r="R181" t="n">
-        <v>7323640</v>
+        <v>7323770</v>
       </c>
       <c r="S181" t="n">
         <v>15</v>
@@ -18904,7 +18906,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>118684515</v>
+        <v>118683764</v>
       </c>
       <c r="B182" t="n">
         <v>79946</v>
@@ -18935,17 +18937,17 @@
       <c r="I182" t="inlineStr"/>
       <c r="P182" t="inlineStr">
         <is>
-          <t>Larsklemetmyran, Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>696823</v>
+        <v>697005</v>
       </c>
       <c r="R182" t="n">
-        <v>7323553</v>
+        <v>7323759</v>
       </c>
       <c r="S182" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T182" t="inlineStr">
         <is>
@@ -18989,12 +18991,12 @@
       <c r="AT182" t="inlineStr"/>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr">
@@ -19005,7 +19007,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>118684516</v>
+        <v>118683765</v>
       </c>
       <c r="B183" t="n">
         <v>79946</v>
@@ -19036,17 +19038,17 @@
       <c r="I183" t="inlineStr"/>
       <c r="P183" t="inlineStr">
         <is>
-          <t>Larsklemetmyran, Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>697059</v>
+        <v>696852</v>
       </c>
       <c r="R183" t="n">
-        <v>7323655</v>
+        <v>7323640</v>
       </c>
       <c r="S183" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T183" t="inlineStr">
         <is>
@@ -19090,12 +19092,12 @@
       <c r="AT183" t="inlineStr"/>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr">
@@ -19106,7 +19108,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>118686836</v>
+        <v>118684515</v>
       </c>
       <c r="B184" t="n">
         <v>79946</v>
@@ -19137,17 +19139,17 @@
       <c r="I184" t="inlineStr"/>
       <c r="P184" t="inlineStr">
         <is>
-          <t>Avvanm, Pi lm</t>
+          <t>Larsklemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>696835</v>
+        <v>696823</v>
       </c>
       <c r="R184" t="n">
-        <v>7323611</v>
+        <v>7323553</v>
       </c>
       <c r="S184" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T184" t="inlineStr">
         <is>
@@ -19191,12 +19193,12 @@
       <c r="AT184" t="inlineStr"/>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr">
@@ -19207,10 +19209,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>118671958</v>
+        <v>118684516</v>
       </c>
       <c r="B185" t="n">
-        <v>78334</v>
+        <v>79946</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -19218,34 +19220,34 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
       <c r="P185" t="inlineStr">
         <is>
-          <t>Anna-Lisabäcken, Anna-Lisabäcken, Pi lm</t>
+          <t>Larsklemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>696938</v>
+        <v>697059</v>
       </c>
       <c r="R185" t="n">
-        <v>7323662</v>
+        <v>7323655</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19292,12 +19294,12 @@
       <c r="AT185" t="inlineStr"/>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>Alexander Singer, Brian Johnson, Daniel Rutschman, Torun Ingrid Maria Jacobsson, Julia Lea Falk, Lisa Requin, Sofia Hamrin, Michaela Ehmann, Evalena Sköld, Tyr Nilsson, Bertil Svensson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr">
@@ -19308,10 +19310,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>118682714</v>
+        <v>118686836</v>
       </c>
       <c r="B186" t="n">
-        <v>78334</v>
+        <v>79946</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -19319,37 +19321,37 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>6487</v>
+        <v>6453</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
       <c r="P186" t="inlineStr">
         <is>
-          <t>Lars-Klemetmyran, Pi lm</t>
+          <t>Avvanm, Pi lm</t>
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>697025</v>
+        <v>696835</v>
       </c>
       <c r="R186" t="n">
-        <v>7323625</v>
+        <v>7323611</v>
       </c>
       <c r="S186" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T186" t="inlineStr">
         <is>
@@ -19393,12 +19395,12 @@
       <c r="AT186" t="inlineStr"/>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr">
@@ -19409,7 +19411,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>118682810</v>
+        <v>118671958</v>
       </c>
       <c r="B187" t="n">
         <v>78334</v>
@@ -19440,17 +19442,17 @@
       <c r="I187" t="inlineStr"/>
       <c r="P187" t="inlineStr">
         <is>
-          <t>Lars-Klemets Myren, Pi lm</t>
+          <t>Anna-Lisabäcken, Anna-Lisabäcken, Pi lm</t>
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>697035</v>
+        <v>696938</v>
       </c>
       <c r="R187" t="n">
-        <v>7323488</v>
+        <v>7323662</v>
       </c>
       <c r="S187" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T187" t="inlineStr">
         <is>
@@ -19488,19 +19490,18 @@
       <c r="AE187" t="b">
         <v>0</v>
       </c>
-      <c r="AF187" t="inlineStr"/>
       <c r="AG187" t="b">
         <v>0</v>
       </c>
       <c r="AT187" t="inlineStr"/>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>Bertil Svensson</t>
+          <t>Alexander Singer, Brian Johnson, Daniel Rutschman, Torun Ingrid Maria Jacobsson, Julia Lea Falk, Lisa Requin, Sofia Hamrin, Michaela Ehmann, Evalena Sköld, Tyr Nilsson, Bertil Svensson</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr">
@@ -19511,7 +19512,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>118683015</v>
+        <v>118682714</v>
       </c>
       <c r="B188" t="n">
         <v>78334</v>
@@ -19542,17 +19543,17 @@
       <c r="I188" t="inlineStr"/>
       <c r="P188" t="inlineStr">
         <is>
-          <t>Lars Klemet myran, Pi lm</t>
+          <t>Lars-Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>696832</v>
+        <v>697025</v>
       </c>
       <c r="R188" t="n">
-        <v>7323503</v>
+        <v>7323625</v>
       </c>
       <c r="S188" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T188" t="inlineStr">
         <is>
@@ -19596,12 +19597,12 @@
       <c r="AT188" t="inlineStr"/>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr">
@@ -19612,7 +19613,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>118683016</v>
+        <v>118682810</v>
       </c>
       <c r="B189" t="n">
         <v>78334</v>
@@ -19643,14 +19644,14 @@
       <c r="I189" t="inlineStr"/>
       <c r="P189" t="inlineStr">
         <is>
-          <t>Lars Klemet myran, Pi lm</t>
+          <t>Lars-Klemets Myren, Pi lm</t>
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>697007</v>
+        <v>697035</v>
       </c>
       <c r="R189" t="n">
-        <v>7323621</v>
+        <v>7323488</v>
       </c>
       <c r="S189" t="n">
         <v>15</v>
@@ -19691,18 +19692,19 @@
       <c r="AE189" t="b">
         <v>0</v>
       </c>
+      <c r="AF189" t="inlineStr"/>
       <c r="AG189" t="b">
         <v>0</v>
       </c>
       <c r="AT189" t="inlineStr"/>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Bertil Svensson</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr">
@@ -19713,7 +19715,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>118683017</v>
+        <v>118683015</v>
       </c>
       <c r="B190" t="n">
         <v>78334</v>
@@ -19748,10 +19750,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>697052</v>
+        <v>696832</v>
       </c>
       <c r="R190" t="n">
-        <v>7323652</v>
+        <v>7323503</v>
       </c>
       <c r="S190" t="n">
         <v>15</v>
@@ -19814,7 +19816,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>118683018</v>
+        <v>118683016</v>
       </c>
       <c r="B191" t="n">
         <v>78334</v>
@@ -19849,10 +19851,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>697057</v>
+        <v>697007</v>
       </c>
       <c r="R191" t="n">
-        <v>7323625</v>
+        <v>7323621</v>
       </c>
       <c r="S191" t="n">
         <v>15</v>
@@ -19915,7 +19917,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>118683019</v>
+        <v>118683017</v>
       </c>
       <c r="B192" t="n">
         <v>78334</v>
@@ -19950,10 +19952,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>697090</v>
+        <v>697052</v>
       </c>
       <c r="R192" t="n">
-        <v>7323674</v>
+        <v>7323652</v>
       </c>
       <c r="S192" t="n">
         <v>15</v>
@@ -19994,7 +19996,6 @@
       <c r="AE192" t="b">
         <v>0</v>
       </c>
-      <c r="AF192" t="inlineStr"/>
       <c r="AG192" t="b">
         <v>0</v>
       </c>
@@ -20017,7 +20018,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>118683795</v>
+        <v>118683018</v>
       </c>
       <c r="B193" t="n">
         <v>78334</v>
@@ -20048,14 +20049,14 @@
       <c r="I193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Lars Klemet myran, Pi lm</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>697023</v>
+        <v>697057</v>
       </c>
       <c r="R193" t="n">
-        <v>7323770</v>
+        <v>7323625</v>
       </c>
       <c r="S193" t="n">
         <v>15</v>
@@ -20096,19 +20097,18 @@
       <c r="AE193" t="b">
         <v>0</v>
       </c>
-      <c r="AF193" t="inlineStr"/>
       <c r="AG193" t="b">
         <v>0</v>
       </c>
       <c r="AT193" t="inlineStr"/>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr">
@@ -20119,7 +20119,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>118683805</v>
+        <v>118683019</v>
       </c>
       <c r="B194" t="n">
         <v>78334</v>
@@ -20150,14 +20150,14 @@
       <c r="I194" t="inlineStr"/>
       <c r="P194" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Lars Klemet myran, Pi lm</t>
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>696843</v>
+        <v>697090</v>
       </c>
       <c r="R194" t="n">
-        <v>7323548</v>
+        <v>7323674</v>
       </c>
       <c r="S194" t="n">
         <v>15</v>
@@ -20198,18 +20198,19 @@
       <c r="AE194" t="b">
         <v>0</v>
       </c>
+      <c r="AF194" t="inlineStr"/>
       <c r="AG194" t="b">
         <v>0</v>
       </c>
       <c r="AT194" t="inlineStr"/>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr">
@@ -20220,7 +20221,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>118683806</v>
+        <v>118683795</v>
       </c>
       <c r="B195" t="n">
         <v>78334</v>
@@ -20255,10 +20256,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>696963</v>
+        <v>697023</v>
       </c>
       <c r="R195" t="n">
-        <v>7323687</v>
+        <v>7323770</v>
       </c>
       <c r="S195" t="n">
         <v>15</v>
@@ -20299,6 +20300,7 @@
       <c r="AE195" t="b">
         <v>0</v>
       </c>
+      <c r="AF195" t="inlineStr"/>
       <c r="AG195" t="b">
         <v>0</v>
       </c>
@@ -20321,7 +20323,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>118683807</v>
+        <v>118683805</v>
       </c>
       <c r="B196" t="n">
         <v>78334</v>
@@ -20356,10 +20358,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>696830</v>
+        <v>696843</v>
       </c>
       <c r="R196" t="n">
-        <v>7323581</v>
+        <v>7323548</v>
       </c>
       <c r="S196" t="n">
         <v>15</v>
@@ -20422,7 +20424,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>118686845</v>
+        <v>118683806</v>
       </c>
       <c r="B197" t="n">
         <v>78334</v>
@@ -20453,17 +20455,17 @@
       <c r="I197" t="inlineStr"/>
       <c r="P197" t="inlineStr">
         <is>
-          <t>Avvanm, Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>696856</v>
+        <v>696963</v>
       </c>
       <c r="R197" t="n">
-        <v>7323627</v>
+        <v>7323687</v>
       </c>
       <c r="S197" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T197" t="inlineStr">
         <is>
@@ -20507,12 +20509,12 @@
       <c r="AT197" t="inlineStr"/>
       <c r="AW197" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX197" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY197" t="inlineStr">
@@ -20523,48 +20525,48 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>118682698</v>
+        <v>118683807</v>
       </c>
       <c r="B198" t="n">
-        <v>57950</v>
+        <v>78334</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>100049</v>
+        <v>6487</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
       <c r="P198" t="inlineStr">
         <is>
-          <t>Lars-Klemetmyran, Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>696847</v>
+        <v>696830</v>
       </c>
       <c r="R198" t="n">
-        <v>7323542</v>
+        <v>7323581</v>
       </c>
       <c r="S198" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T198" t="inlineStr">
         <is>
@@ -20608,12 +20610,12 @@
       <c r="AT198" t="inlineStr"/>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
@@ -20624,10 +20626,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>118672861</v>
+        <v>118686845</v>
       </c>
       <c r="B199" t="n">
-        <v>57953</v>
+        <v>78334</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -20635,37 +20637,37 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>100109</v>
+        <v>6487</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
       <c r="P199" t="inlineStr">
         <is>
-          <t>Anna-Lisabäcken, Anna-Lisabäcken, Pi lm</t>
+          <t>Avvanm, Pi lm</t>
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>697033</v>
+        <v>696856</v>
       </c>
       <c r="R199" t="n">
-        <v>7323478</v>
+        <v>7323627</v>
       </c>
       <c r="S199" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T199" t="inlineStr">
         <is>
@@ -20709,12 +20711,12 @@
       <c r="AT199" t="inlineStr"/>
       <c r="AW199" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX199" t="inlineStr">
         <is>
-          <t>Alexander Singer, Brian Johnson, Daniel Rutschman, Torun Ingrid Maria Jacobsson, Julia Lea Falk, Lisa Requin, Sofia Hamrin, Michaela Ehmann, Evalena Sköld, Tyr Nilsson, Bertil Svensson</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY199" t="inlineStr">
@@ -20725,10 +20727,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>118682772</v>
+        <v>118682698</v>
       </c>
       <c r="B200" t="n">
-        <v>57141</v>
+        <v>57950</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -20736,45 +20738,37 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
-      <c r="K200" t="inlineStr"/>
-      <c r="L200" t="inlineStr"/>
-      <c r="M200" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
-          <t>..., Pi lm</t>
+          <t>Lars-Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>697008</v>
+        <v>696847</v>
       </c>
       <c r="R200" t="n">
-        <v>7323675</v>
+        <v>7323542</v>
       </c>
       <c r="S200" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T200" t="inlineStr">
         <is>
@@ -20818,12 +20812,12 @@
       <c r="AT200" t="inlineStr"/>
       <c r="AW200" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX200" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY200" t="inlineStr">
@@ -20834,45 +20828,45 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>118684517</v>
+        <v>118672861</v>
       </c>
       <c r="B201" t="n">
-        <v>57141</v>
+        <v>57953</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
       <c r="P201" t="inlineStr">
         <is>
-          <t>Larsklemetmyran, Pi lm</t>
+          <t>Anna-Lisabäcken, Anna-Lisabäcken, Pi lm</t>
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>697021</v>
+        <v>697033</v>
       </c>
       <c r="R201" t="n">
-        <v>7323671</v>
+        <v>7323478</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -20919,12 +20913,12 @@
       <c r="AT201" t="inlineStr"/>
       <c r="AW201" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX201" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Alexander Singer, Brian Johnson, Daniel Rutschman, Torun Ingrid Maria Jacobsson, Julia Lea Falk, Lisa Requin, Sofia Hamrin, Michaela Ehmann, Evalena Sköld, Tyr Nilsson, Bertil Svensson</t>
         </is>
       </c>
       <c r="AY201" t="inlineStr">
@@ -20935,48 +20929,56 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>118685851</v>
+        <v>118682772</v>
       </c>
       <c r="B202" t="n">
-        <v>57774</v>
+        <v>57141</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>102976</v>
+        <v>100138</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
+      <c r="K202" t="inlineStr"/>
+      <c r="L202" t="inlineStr"/>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
-          <t>Lars-Klemetmyran, Pi lm</t>
+          <t>..., Pi lm</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>696902</v>
+        <v>697008</v>
       </c>
       <c r="R202" t="n">
-        <v>7323734</v>
+        <v>7323675</v>
       </c>
       <c r="S202" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T202" t="inlineStr">
         <is>
@@ -21020,12 +21022,12 @@
       <c r="AT202" t="inlineStr"/>
       <c r="AW202" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX202" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY202" t="inlineStr">
@@ -21036,10 +21038,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>118682926</v>
+        <v>118684517</v>
       </c>
       <c r="B203" t="n">
-        <v>97989</v>
+        <v>57141</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -21047,34 +21049,34 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
-          <t>Lars-Klemetmyran, Pi lm</t>
+          <t>Larsklemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>696967</v>
+        <v>697021</v>
       </c>
       <c r="R203" t="n">
-        <v>7323736</v>
+        <v>7323671</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21121,12 +21123,12 @@
       <c r="AT203" t="inlineStr"/>
       <c r="AW203" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX203" t="inlineStr">
         <is>
-          <t>Julia Lea Falk, Brian Johnson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY203" t="inlineStr">
@@ -21137,48 +21139,48 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>118683012</v>
+        <v>118685851</v>
       </c>
       <c r="B204" t="n">
-        <v>97989</v>
+        <v>57774</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>221941</v>
+        <v>102976</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
-          <t>Lars Klemet myran, Pi lm</t>
+          <t>Lars-Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>696956</v>
+        <v>696902</v>
       </c>
       <c r="R204" t="n">
-        <v>7323675</v>
+        <v>7323734</v>
       </c>
       <c r="S204" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T204" t="inlineStr">
         <is>
@@ -21222,12 +21224,12 @@
       <c r="AT204" t="inlineStr"/>
       <c r="AW204" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AX204" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AY204" t="inlineStr">
@@ -21238,7 +21240,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>118683784</v>
+        <v>118682926</v>
       </c>
       <c r="B205" t="n">
         <v>97989</v>
@@ -21269,17 +21271,17 @@
       <c r="I205" t="inlineStr"/>
       <c r="P205" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Lars-Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>696996</v>
+        <v>696967</v>
       </c>
       <c r="R205" t="n">
-        <v>7323706</v>
+        <v>7323736</v>
       </c>
       <c r="S205" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T205" t="inlineStr">
         <is>
@@ -21323,12 +21325,12 @@
       <c r="AT205" t="inlineStr"/>
       <c r="AW205" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AX205" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Julia Lea Falk, Brian Johnson</t>
         </is>
       </c>
       <c r="AY205" t="inlineStr">
@@ -21339,7 +21341,7 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>118683785</v>
+        <v>118683012</v>
       </c>
       <c r="B206" t="n">
         <v>97989</v>
@@ -21370,14 +21372,14 @@
       <c r="I206" t="inlineStr"/>
       <c r="P206" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Lars Klemet myran, Pi lm</t>
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>696899</v>
+        <v>696956</v>
       </c>
       <c r="R206" t="n">
-        <v>7323655</v>
+        <v>7323675</v>
       </c>
       <c r="S206" t="n">
         <v>15</v>
@@ -21424,12 +21426,12 @@
       <c r="AT206" t="inlineStr"/>
       <c r="AW206" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AX206" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY206" t="inlineStr">
@@ -21440,7 +21442,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>118684518</v>
+        <v>118683784</v>
       </c>
       <c r="B207" t="n">
         <v>97989</v>
@@ -21471,17 +21473,17 @@
       <c r="I207" t="inlineStr"/>
       <c r="P207" t="inlineStr">
         <is>
-          <t>Larsklemetmyran, Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>696896</v>
+        <v>696996</v>
       </c>
       <c r="R207" t="n">
-        <v>7323658</v>
+        <v>7323706</v>
       </c>
       <c r="S207" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T207" t="inlineStr">
         <is>
@@ -21525,12 +21527,12 @@
       <c r="AT207" t="inlineStr"/>
       <c r="AW207" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX207" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY207" t="inlineStr">
@@ -21541,48 +21543,48 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>118672026</v>
+        <v>118683785</v>
       </c>
       <c r="B208" t="n">
-        <v>79917</v>
+        <v>97989</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>229821</v>
+        <v>221941</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
       <c r="P208" t="inlineStr">
         <is>
-          <t>Anna-Lisabäcken, Anna-Lisabäcken, Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>696971</v>
+        <v>696899</v>
       </c>
       <c r="R208" t="n">
-        <v>7323649</v>
+        <v>7323655</v>
       </c>
       <c r="S208" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T208" t="inlineStr">
         <is>
@@ -21626,12 +21628,12 @@
       <c r="AT208" t="inlineStr"/>
       <c r="AW208" t="inlineStr">
         <is>
-          <t>Alexander Singer</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX208" t="inlineStr">
         <is>
-          <t>Alexander Singer, Brian Johnson, Daniel Rutschman, Torun Ingrid Maria Jacobsson, Julia Lea Falk, Lisa Requin, Sofia Hamrin, Michaela Ehmann, Evalena Sköld, Tyr Nilsson, Bertil Svensson</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY208" t="inlineStr">
@@ -21642,45 +21644,45 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>118682919</v>
+        <v>118684518</v>
       </c>
       <c r="B209" t="n">
-        <v>79917</v>
+        <v>97989</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>229821</v>
+        <v>221941</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
       <c r="P209" t="inlineStr">
         <is>
-          <t>Lars-Klemetmyran, Pi lm</t>
+          <t>Larsklemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>696875</v>
+        <v>696896</v>
       </c>
       <c r="R209" t="n">
-        <v>7323766</v>
+        <v>7323658</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -21727,12 +21729,12 @@
       <c r="AT209" t="inlineStr"/>
       <c r="AW209" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX209" t="inlineStr">
         <is>
-          <t>Julia Lea Falk</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY209" t="inlineStr">
@@ -21743,7 +21745,7 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>118683006</v>
+        <v>118672026</v>
       </c>
       <c r="B210" t="n">
         <v>79917</v>
@@ -21774,17 +21776,17 @@
       <c r="I210" t="inlineStr"/>
       <c r="P210" t="inlineStr">
         <is>
-          <t>Lars Klemet myran, Pi lm</t>
+          <t>Anna-Lisabäcken, Anna-Lisabäcken, Pi lm</t>
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>696855</v>
+        <v>696971</v>
       </c>
       <c r="R210" t="n">
-        <v>7323504</v>
+        <v>7323649</v>
       </c>
       <c r="S210" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T210" t="inlineStr">
         <is>
@@ -21822,19 +21824,18 @@
       <c r="AE210" t="b">
         <v>0</v>
       </c>
-      <c r="AF210" t="inlineStr"/>
       <c r="AG210" t="b">
         <v>0</v>
       </c>
       <c r="AT210" t="inlineStr"/>
       <c r="AW210" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Alexander Singer</t>
         </is>
       </c>
       <c r="AX210" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Alexander Singer, Brian Johnson, Daniel Rutschman, Torun Ingrid Maria Jacobsson, Julia Lea Falk, Lisa Requin, Sofia Hamrin, Michaela Ehmann, Evalena Sköld, Tyr Nilsson, Bertil Svensson</t>
         </is>
       </c>
       <c r="AY210" t="inlineStr">
@@ -21845,7 +21846,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>118683007</v>
+        <v>118682919</v>
       </c>
       <c r="B211" t="n">
         <v>79917</v>
@@ -21876,17 +21877,17 @@
       <c r="I211" t="inlineStr"/>
       <c r="P211" t="inlineStr">
         <is>
-          <t>Lars Klemet myran, Pi lm</t>
+          <t>Lars-Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>697013</v>
+        <v>696875</v>
       </c>
       <c r="R211" t="n">
-        <v>7323628</v>
+        <v>7323766</v>
       </c>
       <c r="S211" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T211" t="inlineStr">
         <is>
@@ -21924,19 +21925,18 @@
       <c r="AE211" t="b">
         <v>0</v>
       </c>
-      <c r="AF211" t="inlineStr"/>
       <c r="AG211" t="b">
         <v>0</v>
       </c>
       <c r="AT211" t="inlineStr"/>
       <c r="AW211" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AX211" t="inlineStr">
         <is>
-          <t>Torun Ingrid Maria Jacobsson</t>
+          <t>Julia Lea Falk</t>
         </is>
       </c>
       <c r="AY211" t="inlineStr">
@@ -21947,7 +21947,7 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>118683008</v>
+        <v>118683006</v>
       </c>
       <c r="B212" t="n">
         <v>79917</v>
@@ -21982,10 +21982,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>697097</v>
+        <v>696855</v>
       </c>
       <c r="R212" t="n">
-        <v>7323675</v>
+        <v>7323504</v>
       </c>
       <c r="S212" t="n">
         <v>15</v>
@@ -22049,7 +22049,7 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>118683009</v>
+        <v>118683007</v>
       </c>
       <c r="B213" t="n">
         <v>79917</v>
@@ -22084,10 +22084,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>697057</v>
+        <v>697013</v>
       </c>
       <c r="R213" t="n">
-        <v>7323625</v>
+        <v>7323628</v>
       </c>
       <c r="S213" t="n">
         <v>15</v>
@@ -22128,6 +22128,7 @@
       <c r="AE213" t="b">
         <v>0</v>
       </c>
+      <c r="AF213" t="inlineStr"/>
       <c r="AG213" t="b">
         <v>0</v>
       </c>
@@ -22150,7 +22151,7 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>118683770</v>
+        <v>118683008</v>
       </c>
       <c r="B214" t="n">
         <v>79917</v>
@@ -22181,14 +22182,14 @@
       <c r="I214" t="inlineStr"/>
       <c r="P214" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Lars Klemet myran, Pi lm</t>
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>696916</v>
+        <v>697097</v>
       </c>
       <c r="R214" t="n">
-        <v>7323554</v>
+        <v>7323675</v>
       </c>
       <c r="S214" t="n">
         <v>15</v>
@@ -22229,18 +22230,19 @@
       <c r="AE214" t="b">
         <v>0</v>
       </c>
+      <c r="AF214" t="inlineStr"/>
       <c r="AG214" t="b">
         <v>0</v>
       </c>
       <c r="AT214" t="inlineStr"/>
       <c r="AW214" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AX214" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY214" t="inlineStr">
@@ -22251,7 +22253,7 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>118683771</v>
+        <v>118683009</v>
       </c>
       <c r="B215" t="n">
         <v>79917</v>
@@ -22282,14 +22284,14 @@
       <c r="I215" t="inlineStr"/>
       <c r="P215" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Lars Klemet myran, Pi lm</t>
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>697006</v>
+        <v>697057</v>
       </c>
       <c r="R215" t="n">
-        <v>7323536</v>
+        <v>7323625</v>
       </c>
       <c r="S215" t="n">
         <v>15</v>
@@ -22336,12 +22338,12 @@
       <c r="AT215" t="inlineStr"/>
       <c r="AW215" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AX215" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Torun Ingrid Maria Jacobsson</t>
         </is>
       </c>
       <c r="AY215" t="inlineStr">
@@ -22352,7 +22354,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>118683772</v>
+        <v>118683770</v>
       </c>
       <c r="B216" t="n">
         <v>79917</v>
@@ -22387,10 +22389,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>697029</v>
+        <v>696916</v>
       </c>
       <c r="R216" t="n">
-        <v>7323644</v>
+        <v>7323554</v>
       </c>
       <c r="S216" t="n">
         <v>15</v>
@@ -22453,7 +22455,7 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>118683774</v>
+        <v>118683771</v>
       </c>
       <c r="B217" t="n">
         <v>79917</v>
@@ -22488,10 +22490,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>697096</v>
+        <v>697006</v>
       </c>
       <c r="R217" t="n">
-        <v>7323682</v>
+        <v>7323536</v>
       </c>
       <c r="S217" t="n">
         <v>15</v>
@@ -22554,7 +22556,7 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>118683775</v>
+        <v>118683772</v>
       </c>
       <c r="B218" t="n">
         <v>79917</v>
@@ -22589,10 +22591,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>697098</v>
+        <v>697029</v>
       </c>
       <c r="R218" t="n">
-        <v>7323697</v>
+        <v>7323644</v>
       </c>
       <c r="S218" t="n">
         <v>15</v>
@@ -22655,7 +22657,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>118683776</v>
+        <v>118683774</v>
       </c>
       <c r="B219" t="n">
         <v>79917</v>
@@ -22690,10 +22692,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>697001</v>
+        <v>697096</v>
       </c>
       <c r="R219" t="n">
-        <v>7323753</v>
+        <v>7323682</v>
       </c>
       <c r="S219" t="n">
         <v>15</v>
@@ -22756,7 +22758,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>118683777</v>
+        <v>118683775</v>
       </c>
       <c r="B220" t="n">
         <v>79917</v>
@@ -22791,10 +22793,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>697010</v>
+        <v>697098</v>
       </c>
       <c r="R220" t="n">
-        <v>7323702</v>
+        <v>7323697</v>
       </c>
       <c r="S220" t="n">
         <v>15</v>
@@ -22857,7 +22859,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>118683778</v>
+        <v>118683776</v>
       </c>
       <c r="B221" t="n">
         <v>79917</v>
@@ -22892,10 +22894,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>696970</v>
+        <v>697001</v>
       </c>
       <c r="R221" t="n">
-        <v>7323681</v>
+        <v>7323753</v>
       </c>
       <c r="S221" t="n">
         <v>15</v>
@@ -22958,7 +22960,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>118683779</v>
+        <v>118683777</v>
       </c>
       <c r="B222" t="n">
         <v>79917</v>
@@ -22993,10 +22995,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>696901</v>
+        <v>697010</v>
       </c>
       <c r="R222" t="n">
-        <v>7323660</v>
+        <v>7323702</v>
       </c>
       <c r="S222" t="n">
         <v>15</v>
@@ -23059,7 +23061,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>118683780</v>
+        <v>118683778</v>
       </c>
       <c r="B223" t="n">
         <v>79917</v>
@@ -23094,10 +23096,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>696853</v>
+        <v>696970</v>
       </c>
       <c r="R223" t="n">
-        <v>7323635</v>
+        <v>7323681</v>
       </c>
       <c r="S223" t="n">
         <v>15</v>
@@ -23160,7 +23162,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>118683781</v>
+        <v>118683779</v>
       </c>
       <c r="B224" t="n">
         <v>79917</v>
@@ -23195,10 +23197,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>696838</v>
+        <v>696901</v>
       </c>
       <c r="R224" t="n">
-        <v>7323602</v>
+        <v>7323660</v>
       </c>
       <c r="S224" t="n">
         <v>15</v>
@@ -23261,7 +23263,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>118686837</v>
+        <v>118683780</v>
       </c>
       <c r="B225" t="n">
         <v>79917</v>
@@ -23292,17 +23294,17 @@
       <c r="I225" t="inlineStr"/>
       <c r="P225" t="inlineStr">
         <is>
-          <t>Avvanm, Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>696859</v>
+        <v>696853</v>
       </c>
       <c r="R225" t="n">
-        <v>7323641</v>
+        <v>7323635</v>
       </c>
       <c r="S225" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T225" t="inlineStr">
         <is>
@@ -23346,12 +23348,12 @@
       <c r="AT225" t="inlineStr"/>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr">
@@ -23362,10 +23364,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>118686838</v>
+        <v>118683781</v>
       </c>
       <c r="B226" t="n">
-        <v>79350</v>
+        <v>79917</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -23373,37 +23375,37 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>260591</v>
+        <v>229821</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
         <is>
-          <t>Avvanm, Pi lm</t>
+          <t>Lars Klemetmyran, Pi lm</t>
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>696935</v>
+        <v>696838</v>
       </c>
       <c r="R226" t="n">
-        <v>7323600</v>
+        <v>7323602</v>
       </c>
       <c r="S226" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="T226" t="inlineStr">
         <is>
@@ -23447,12 +23449,12 @@
       <c r="AT226" t="inlineStr"/>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>Sofia Hamrin</t>
+          <t>Tyr Nilsson</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
@@ -23463,46 +23465,48 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>118683788</v>
+        <v>118686837</v>
       </c>
       <c r="B227" t="n">
-        <v>80221</v>
+        <v>79917</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>266179</v>
+        <v>229821</v>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Lecidea subhumida</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Vain.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
-      <c r="J227" t="inlineStr"/>
-      <c r="K227" t="inlineStr"/>
-      <c r="N227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Avvanm, Pi lm</t>
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>697094</v>
+        <v>696859</v>
       </c>
       <c r="R227" t="n">
-        <v>7323681</v>
+        <v>7323641</v>
       </c>
       <c r="S227" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T227" t="inlineStr">
         <is>
@@ -23534,30 +23538,24 @@
           <t>2024-07-25</t>
         </is>
       </c>
-      <c r="AC227" t="inlineStr">
-        <is>
-          <t>På gren på gammal tallåga</t>
-        </is>
-      </c>
       <c r="AD227" t="b">
         <v>0</v>
       </c>
       <c r="AE227" t="b">
         <v>0</v>
       </c>
-      <c r="AF227" t="inlineStr"/>
       <c r="AG227" t="b">
         <v>0</v>
       </c>
       <c r="AT227" t="inlineStr"/>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>Tyr Nilsson</t>
+          <t>Sofia Hamrin</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr">
@@ -23568,46 +23566,48 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>118683789</v>
+        <v>118686838</v>
       </c>
       <c r="B228" t="n">
-        <v>80221</v>
+        <v>79350</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>266179</v>
+        <v>260591</v>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Lecidea subhumida</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Vain.</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
-      <c r="J228" t="inlineStr"/>
-      <c r="K228" t="inlineStr"/>
-      <c r="N228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
-          <t>Lars Klemetmyran, Pi lm</t>
+          <t>Avvanm, Pi lm</t>
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>696910</v>
+        <v>696935</v>
       </c>
       <c r="R228" t="n">
-        <v>7323669</v>
+        <v>7323600</v>
       </c>
       <c r="S228" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="T228" t="inlineStr">
         <is>
@@ -23639,33 +23639,237 @@
           <t>2024-07-25</t>
         </is>
       </c>
-      <c r="AC228" t="inlineStr">
-        <is>
-          <t>På gren på gammal tallåga</t>
-        </is>
-      </c>
       <c r="AD228" t="b">
         <v>0</v>
       </c>
       <c r="AE228" t="b">
         <v>0</v>
       </c>
-      <c r="AF228" t="inlineStr"/>
       <c r="AG228" t="b">
         <v>0</v>
       </c>
       <c r="AT228" t="inlineStr"/>
       <c r="AW228" t="inlineStr">
         <is>
+          <t>Sofia Hamrin</t>
+        </is>
+      </c>
+      <c r="AX228" t="inlineStr">
+        <is>
+          <t>Sofia Hamrin</t>
+        </is>
+      </c>
+      <c r="AY228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>118683788</v>
+      </c>
+      <c r="B229" t="n">
+        <v>80221</v>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E229" t="n">
+        <v>266179</v>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>Lecidea subhumida</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Vain.</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr"/>
+      <c r="J229" t="inlineStr"/>
+      <c r="K229" t="inlineStr"/>
+      <c r="N229" t="inlineStr"/>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>Lars Klemetmyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q229" t="n">
+        <v>697094</v>
+      </c>
+      <c r="R229" t="n">
+        <v>7323681</v>
+      </c>
+      <c r="S229" t="n">
+        <v>15</v>
+      </c>
+      <c r="T229" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U229" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V229" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W229" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y229" t="inlineStr">
+        <is>
+          <t>2024-07-25</t>
+        </is>
+      </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>2024-07-25</t>
+        </is>
+      </c>
+      <c r="AC229" t="inlineStr">
+        <is>
+          <t>På gren på gammal tallåga</t>
+        </is>
+      </c>
+      <c r="AD229" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE229" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF229" t="inlineStr"/>
+      <c r="AG229" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT229" t="inlineStr"/>
+      <c r="AW229" t="inlineStr">
+        <is>
           <t>Tyr Nilsson</t>
         </is>
       </c>
-      <c r="AX228" t="inlineStr">
+      <c r="AX229" t="inlineStr">
         <is>
           <t>Tyr Nilsson</t>
         </is>
       </c>
-      <c r="AY228" t="inlineStr">
+      <c r="AY229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>118683789</v>
+      </c>
+      <c r="B230" t="n">
+        <v>80221</v>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E230" t="n">
+        <v>266179</v>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Lecidea subhumida</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>Vain.</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr"/>
+      <c r="J230" t="inlineStr"/>
+      <c r="K230" t="inlineStr"/>
+      <c r="N230" t="inlineStr"/>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>Lars Klemetmyran, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q230" t="n">
+        <v>696910</v>
+      </c>
+      <c r="R230" t="n">
+        <v>7323669</v>
+      </c>
+      <c r="S230" t="n">
+        <v>15</v>
+      </c>
+      <c r="T230" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V230" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W230" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y230" t="inlineStr">
+        <is>
+          <t>2024-07-25</t>
+        </is>
+      </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>2024-07-25</t>
+        </is>
+      </c>
+      <c r="AC230" t="inlineStr">
+        <is>
+          <t>På gren på gammal tallåga</t>
+        </is>
+      </c>
+      <c r="AD230" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE230" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF230" t="inlineStr"/>
+      <c r="AG230" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT230" t="inlineStr"/>
+      <c r="AW230" t="inlineStr">
+        <is>
+          <t>Tyr Nilsson</t>
+        </is>
+      </c>
+      <c r="AX230" t="inlineStr">
+        <is>
+          <t>Tyr Nilsson</t>
+        </is>
+      </c>
+      <c r="AY230" t="inlineStr">
         <is>
           <t xml:space="preserve">Forskningsresan i Naturvårdens Utmarker 2024 Norrbottens län </t>
         </is>
